--- a/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
+++ b/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
@@ -254,6 +254,9 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -264,7 +267,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -274,10 +277,7 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2744,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2760,183 +2760,341 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
         <is>
+          <t>Proactividad comercial</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Abr 2026</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Var Rec 2A (%)</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n">
+        <v>-15.34</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>-11.95</v>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>≥0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Var MO 2A (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>-14.65</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>≥0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Calidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>CAL1SEM</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B10" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>5,0</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Procesos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Productividad (%)</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B14" s="26" t="n">
         <v>119.83</v>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>120%</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>Var Rec 2A (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="n">
-        <v>-15.34</v>
-      </c>
-      <c r="C6" s="31" t="n">
-        <v>-11.95</v>
-      </c>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>Var MO 2A (%)</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="n">
-        <v>-14.65</v>
-      </c>
-      <c r="C7" s="31" t="n">
-        <v>-11.7</v>
-      </c>
-      <c r="D7" s="27" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Carrocería</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>ICC Carrocería</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>ICC Personas</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Rankings de marca</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>ICC posición global</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>Horch Lauden</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B27" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C27" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>≤50</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>ICC posición global</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>16</v>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>ICC Carrocería</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>ICC Personas</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2972,22 +3130,22 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Referencia</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Positivo si...</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Mejorar si...</t>
         </is>

--- a/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
+++ b/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
@@ -2803,7 +2803,7 @@
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>≥0%</t>
+          <t>&gt;8%</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D6" s="28" t="inlineStr">
         <is>
-          <t>≥0%</t>
+          <t>&gt;6%</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="D10" s="28" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>≥6</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D27" s="28" t="inlineStr">
         <is>
-          <t>≤50</t>
+          <t>&lt;20</t>
         </is>
       </c>
     </row>

--- a/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
+++ b/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
@@ -2744,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3086,13 +3086,63 @@
         </is>
       </c>
     </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Cuadro CX</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>CX total (/8)</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>≥7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A16:D16"/>
   </mergeCells>

--- a/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
+++ b/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
@@ -11,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mar 20261" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abr 2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolución" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objetivos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,14 +97,8 @@
       <color rgb="00FFD700"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="008B6914"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -147,21 +140,6 @@
         <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -189,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -282,21 +260,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3148,174 +3111,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>Objetivos y umbrales de referencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
-        <is>
-          <t>Objetivo de productividad específico para esta instalación: 120%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>Métrica</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Referencia</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>Positivo si...</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>Mejorar si...</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
-        <is>
-          <t>CAL1SEM</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>≥5,0</t>
-        </is>
-      </c>
-      <c r="C6" s="35" t="inlineStr">
-        <is>
-          <t>≥5,0</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>&lt;5,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
-        <is>
-          <t>Productividad</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>120%</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="inlineStr">
-        <is>
-          <t>≥120%</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>&lt;120%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>Var Rec 2A</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-      <c r="C8" s="35" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>&lt;0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
-        <is>
-          <t>Var MO 2A</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-      <c r="C9" s="35" t="inlineStr">
-        <is>
-          <t>≥0%</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>&lt;0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>Horch Lauden (pos)</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>≤50 aceptable</t>
-        </is>
-      </c>
-      <c r="C10" s="35" t="inlineStr">
-        <is>
-          <t>≤20 dest. / ≤50 acept.</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>&gt;50 — requiere atención</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
+++ b/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
@@ -2432,7 +2432,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Fecha: 06/05/2026</t>
+          <t>Fecha: 07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,6 +2590,11 @@
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Grado de cumplimentación</t>
         </is>
@@ -2604,6 +2609,7 @@
       <c r="B27" s="9" t="inlineStr"/>
       <c r="C27" s="9" t="inlineStr"/>
       <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
@@ -2614,6 +2620,7 @@
       <c r="B28" s="13" t="inlineStr"/>
       <c r="C28" s="13" t="inlineStr"/>
       <c r="D28" s="13" t="inlineStr"/>
+      <c r="E28" s="13" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -2624,6 +2631,7 @@
       <c r="B29" s="9" t="inlineStr"/>
       <c r="C29" s="9" t="inlineStr"/>
       <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
@@ -2634,6 +2642,7 @@
       <c r="B30" s="13" t="inlineStr"/>
       <c r="C30" s="13" t="inlineStr"/>
       <c r="D30" s="13" t="inlineStr"/>
+      <c r="E30" s="13" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
@@ -2644,6 +2653,7 @@
       <c r="B31" s="9" t="inlineStr"/>
       <c r="C31" s="9" t="inlineStr"/>
       <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="9" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
@@ -2654,6 +2664,7 @@
       <c r="B32" s="13" t="inlineStr"/>
       <c r="C32" s="13" t="inlineStr"/>
       <c r="D32" s="13" t="inlineStr"/>
+      <c r="E32" s="13" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
@@ -2664,6 +2675,7 @@
       <c r="B33" s="9" t="inlineStr"/>
       <c r="C33" s="9" t="inlineStr"/>
       <c r="D33" s="9" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
@@ -2674,6 +2686,7 @@
       <c r="B34" s="13" t="inlineStr"/>
       <c r="C34" s="13" t="inlineStr"/>
       <c r="D34" s="13" t="inlineStr"/>
+      <c r="E34" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -3027,7 +3040,7 @@
       </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>&lt;20</t>
         </is>
       </c>
     </row>

--- a/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
+++ b/informes/informe_seguimiento_pericles_canarias_chapa.xlsx
@@ -2404,7 +2404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2560,140 +2560,196 @@
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Sin datos registrados</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>PUNTOS POSITIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Satisfacción General (CEM Q4): 4,80 — 2/2 pts  |  Referencia: 0pts &lt;4,60 | 1pt ≥4,60 | 2pts ≥4,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>PUNTOS A MEJORAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Medidas de Servicio (EC28): 1,72% — 1/2 pts  |  Referencia: 0pts &gt;5% | 1pt ≤5% | 2pts ≤1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Información Proceso (TRS): 87,50% — 1/2 pts  |  Referencia: 0pts &lt;80% | 1pt ≥80% | 2pts ≥90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Conectividad Posventa: 38,71% — 1/2 pts  |  Referencia: 0pts &lt;25% | 1pt ≥25% | 2pts ≥45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>6. Tareas pendientes</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Fecha límite</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>Grado de cumplimentación</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Chapa Express</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr"/>
-      <c r="C27" s="9" t="inlineStr"/>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Reparacion de Lunas</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr"/>
-      <c r="C28" s="13" t="inlineStr"/>
-      <c r="D28" s="13" t="inlineStr"/>
-      <c r="E28" s="13" t="inlineStr"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr"/>
+      <c r="C33" s="13" t="inlineStr"/>
+      <c r="D33" s="13" t="inlineStr"/>
+      <c r="E33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Meter todos los códigos de reparación</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr"/>
-      <c r="C29" s="9" t="inlineStr"/>
-      <c r="D29" s="9" t="inlineStr"/>
-      <c r="E29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr"/>
+      <c r="E34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Recuperación de siniestros</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr"/>
-      <c r="C30" s="13" t="inlineStr"/>
-      <c r="D30" s="13" t="inlineStr"/>
-      <c r="E30" s="13" t="inlineStr"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr"/>
+      <c r="C35" s="13" t="inlineStr"/>
+      <c r="D35" s="13" t="inlineStr"/>
+      <c r="E35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Mínimo empatar en Junio en Mano de obra y recambios.</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr"/>
-      <c r="C31" s="9" t="inlineStr"/>
-      <c r="D31" s="9" t="inlineStr"/>
-      <c r="E31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr"/>
+      <c r="D36" s="9" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Productividad 120%</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr"/>
-      <c r="C32" s="13" t="inlineStr"/>
-      <c r="D32" s="13" t="inlineStr"/>
-      <c r="E32" s="13" t="inlineStr"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr"/>
+      <c r="C37" s="13" t="inlineStr"/>
+      <c r="D37" s="13" t="inlineStr"/>
+      <c r="E37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Tiempo de ciclo de carrocería.</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr"/>
-      <c r="C33" s="9" t="inlineStr"/>
-      <c r="D33" s="9" t="inlineStr"/>
-      <c r="E33" s="9" t="inlineStr"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr"/>
+      <c r="C38" s="9" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>Atentos a la formación</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr"/>
-      <c r="C34" s="13" t="inlineStr"/>
-      <c r="D34" s="13" t="inlineStr"/>
-      <c r="E34" s="13" t="inlineStr"/>
+      <c r="B39" s="13" t="inlineStr"/>
+      <c r="C39" s="13" t="inlineStr"/>
+      <c r="D39" s="13" t="inlineStr"/>
+      <c r="E39" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="24">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A5:F5"/>
@@ -2701,13 +2757,17 @@
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B24:F24"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="B26:F26"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3100,10 +3160,8 @@
       <c r="B31" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C31" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="D31" s="28" t="inlineStr">
         <is>
